--- a/data/courses_data.xlsx
+++ b/data/courses_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="176">
   <si>
     <t>program</t>
   </si>
@@ -28,6 +28,9 @@
     <t>description</t>
   </si>
   <si>
+    <t>modules</t>
+  </si>
+  <si>
     <t>urlslug</t>
   </si>
   <si>
@@ -266,6 +269,96 @@
   </si>
   <si>
     <t>Covers Digital Marketing Foundations &amp; Strategy, SEO Specialist Track, Website Development &amp; Landing Pages, Social Media Marketing &amp; Management, Content Marketing &amp; Copywriting, plus 7 more modules, building practical, job-ready skills in Advanced Digital Marketing Performance.</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API); Git &amp; SDLC; Data Structures &amp; Algorithms (Python); Machine Learning (Supervised &amp; Unsupervised); Artificial Intelligence; Database (MySQL); Python Libraries(Numpy, Pandas, Matplotlib, Seaborn); Data Visualization (Power BI); Cloud (Azure)</t>
+  </si>
+  <si>
+    <t>Figma, HTML, CSS, JavaScript; Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API); Git &amp; SDLC; Data Structures &amp; Algorithms (Python); Mobile App (Flutter)</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Database (Mongo DB); Frontend Library (React. JS); Framework (Node js with REST API); Git &amp; SDLC; Mobile App (React Native)</t>
+  </si>
+  <si>
+    <t>Adv Excel with Dashboard; Statistics &amp; Mathematics for Data Analytics</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API); Git &amp; SDLC; Data Structures &amp; Algorithms (Python); Machine Learning (Supervised &amp; Unsupervised); Artificial Intelligence; Database (MySQL); Python Libraries(Numpy, Pandas, Matplotlib, Seaborn); Data Visualization (Power BI); Cloud (Azure); Mobile App (Flutter)</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API); Git &amp; SDLC; Data Structures &amp; Algorithms (Python); Machine Learning (Supervised &amp; Unsupervised); Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Java); Frontend Library (React. JS); Framework (Springboot); Git &amp; SDLC; Data Structures &amp; Algorithms (Python)</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Database (Mongo DB); Frontend Library (React. JS); Framework (Node js with REST API); Git &amp; SDLC</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Java); Frontend Library (React. JS); Framework (Springboot with API); Git &amp; SDLC; Data Structures &amp; Algorithms (Python); Mobile App (Flutter)</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Java); Framework (Springboot with CRUD); Data Structures &amp; Algorithms (with Java)</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Database (Mongo DB); Frontend Library (React. JS); Framework (Node js with REST API)</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API)</t>
+  </si>
+  <si>
+    <t>Figma, HTML, CSS, JavaScript; Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API)</t>
+  </si>
+  <si>
+    <t>Foundation; Security Essentials; Ethical Hacking Methodology; Web Application Security; Security Operations &amp; Incident Response; AWS Solution Architect — Security Focus; Advanced VAPT; Mobile &amp; Digital Forensics; Red Team Operations; Bug Bounty &amp; Hacker Mindset; Build Modern Infrastructure; Automate the Platform; AI Foundations for Security Professionals; Generative AI in Practice; AI Agents &amp; AI Security</t>
+  </si>
+  <si>
+    <t>Foundation; Security Essentials; Ethical Hacking Methodology; Web Application Security; Security Operations &amp; Incident Response; AWS Solution Architect — Security Focus; Advanced VAPT; Mobile &amp; Digital Forensics; Red Team Operations; Bug Bounty &amp; Hacker Mindset</t>
+  </si>
+  <si>
+    <t>Foundation; Security Essentials; Ethical Hacking Methodology; Web Application Security; Security Operations &amp; Incident Response</t>
+  </si>
+  <si>
+    <t>Python Fundamentals; Data Structures &amp; Data Fundamentals; Machine Learning Foundations; Data Analytics &amp; Visualization; Computer Vision; AI/ML Foundations &amp; Deep Learning; GenAI Foundations; Vibe Coding / AI-Assisted Development; LLM Application Development; RAG; AI Agents; Advanced Agentic AI; MLOps / AIOps; SQL &amp; Database Management; AWS / Cloud; IoT &amp; Embedded Systems; AI + IoT Integration; Full-Stack Development; AI Product Development; AI Engineering; Robotics &amp; Smart Systems; Deployment &amp; Production; Capstone &amp; Industry Project</t>
+  </si>
+  <si>
+    <t>Python Fundamentals; Machine Learning Foundations; GenAI Foundations; Vibe Coding / AI-Assisted Development; AI Product Development</t>
+  </si>
+  <si>
+    <t>Python Fundamentals; Machine Learning Foundations; Computer Vision; IoT &amp; Embedded Systems; AI + IoT Integration</t>
+  </si>
+  <si>
+    <t>Python Fundamentals; AI/ML Foundations &amp; Deep Learning; GenAI Foundations; LLM Application Development; RAG; AI Agents; Advanced Agentic AI; AWS / Cloud</t>
+  </si>
+  <si>
+    <t>Python Fundamentals; Data Structures &amp; Data Fundamentals; Data Analytics &amp; Visualization; GenAI Foundations; Vibe Coding / AI-Assisted Development; LLM Application Development; RAG; AI Agents; MLOps / AIOps; SQL &amp; Database Management</t>
+  </si>
+  <si>
+    <t>Python Fundamentals; Data Structures &amp; Data Fundamentals; Machine Learning Foundations; Data Analytics &amp; Visualization; AI/ML Foundations &amp; Deep Learning; GenAI Foundations; LLM Application Development; RAG; AI Agents; MLOps / AIOps; AWS / Cloud; IoT &amp; Embedded Systems; AI + IoT Integration</t>
+  </si>
+  <si>
+    <t>Full-Stack Development; AI Product Development; AI Engineering; Robotics &amp; Smart Systems; Deployment &amp; Production; Capstone &amp; Industry Project</t>
+  </si>
+  <si>
+    <t>GenAI Foundations; LLM Application Development; RAG; AI Agents; Advanced Agentic AI; IoT &amp; Embedded Systems; AI + IoT Integration; Full-Stack Development</t>
+  </si>
+  <si>
+    <t>Data Analytics Foundations; Advanced Excel; Statistics for Data Analytics; Python Programming for Analytics; NumPy &amp; Pandas; Data Visualization with Python; SQL &amp; Database Analytics; Power BI &amp; Business Intelligence; Exploratory Data Analysis (EDA); ETL &amp; Data Preparation; Digital Business Analytics; Digital Marketing Analytics; GenAI Tools for Data Analytics; Graphics &amp; Video for Digital Analytics; Advanced Analytics Projects; Industry Internship / Capstone</t>
+  </si>
+  <si>
+    <t>Data Analytics Foundations; Advanced Excel; Statistics for Data Analytics; Python Programming for Analytics; Power BI &amp; Business Intelligence</t>
+  </si>
+  <si>
+    <t>Data Analytics Foundations; Advanced Excel; Statistics for Data Analytics; Python Programming for Analytics; NumPy &amp; Pandas; Data Visualization with Python; SQL &amp; Database Analytics; Power BI &amp; Business Intelligence; Exploratory Data Analysis (EDA); ETL &amp; Data Preparation</t>
+  </si>
+  <si>
+    <t>Digital Marketing Foundations &amp; Strategy; SEO Specialist Track; Website Development &amp; Landing Pages; Social Media Marketing &amp; Management; Content Marketing &amp; Copywriting; Lead Generation, Landing Pages &amp; Conversion; Search Engine Marketing (SEM) &amp; Paid Search; Online Display &amp; Remarketing; E-Commerce &amp; Online Sales Marketing; Video Marketing &amp; YouTube; Mobile App Marketing; Google Ads Ecosystem: Discovery, Performance Max &amp; Search; Growth, Reputation, Email &amp; Messaging; Freelancing, Portfolio, Resume &amp; Interview Readiness; AI-Powered Digital Marketing &amp; Career Growth</t>
+  </si>
+  <si>
+    <t>Digital Marketing Foundations &amp; Strategy; SEO Specialist Track; Website Development &amp; Landing Pages; Social Media Marketing &amp; Management; Content Marketing &amp; Copywriting; Lead Generation, Landing Pages &amp; Conversion; Search Engine Marketing (SEM) &amp; Paid Search; Online Display &amp; Remarketing</t>
+  </si>
+  <si>
+    <t>Digital Marketing Foundations &amp; Strategy; SEO Specialist Track; Website Development &amp; Landing Pages; Social Media Marketing &amp; Management; Content Marketing &amp; Copywriting; Lead Generation, Landing Pages &amp; Conversion; Search Engine Marketing (SEM) &amp; Paid Search; Online Display &amp; Remarketing; E-Commerce &amp; Online Sales Marketing; Video Marketing &amp; YouTube; Mobile App Marketing; Google Ads Ecosystem: Discovery, Performance Max &amp; Search</t>
   </si>
   <si>
     <t>full-stack-data-science-with-ai-course</t>
@@ -780,10 +873,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -823,562 +916,658 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" t="s">
+        <v>115</v>
+      </c>
+      <c r="L2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" t="s">
+        <v>118</v>
+      </c>
+      <c r="L5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" t="s">
+        <v>119</v>
+      </c>
+      <c r="L6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" t="s">
+        <v>120</v>
+      </c>
+      <c r="L7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F8" t="s">
+        <v>121</v>
+      </c>
+      <c r="L8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" t="s">
+        <v>122</v>
+      </c>
+      <c r="L9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" t="s">
+        <v>123</v>
+      </c>
+      <c r="L10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" t="s">
+        <v>124</v>
+      </c>
+      <c r="L11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L12" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" t="s">
+        <v>126</v>
+      </c>
+      <c r="L13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" t="s">
+        <v>127</v>
+      </c>
+      <c r="L14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" t="s">
+        <v>98</v>
+      </c>
+      <c r="F15" t="s">
+        <v>128</v>
+      </c>
+      <c r="L15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" t="s">
+        <v>129</v>
+      </c>
+      <c r="L16" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" t="s">
+        <v>130</v>
+      </c>
+      <c r="L17" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" t="s">
+        <v>131</v>
+      </c>
+      <c r="L18" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" t="s">
+        <v>102</v>
+      </c>
+      <c r="F19" t="s">
+        <v>132</v>
+      </c>
+      <c r="L19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" t="s">
+        <v>103</v>
+      </c>
+      <c r="F20" t="s">
+        <v>133</v>
+      </c>
+      <c r="L20" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" t="s">
+        <v>134</v>
+      </c>
+      <c r="L21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s">
+        <v>105</v>
+      </c>
+      <c r="F22" t="s">
+        <v>135</v>
+      </c>
+      <c r="L22" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" t="s">
+        <v>136</v>
+      </c>
+      <c r="L23" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" t="s">
+        <v>107</v>
+      </c>
+      <c r="F24" t="s">
+        <v>137</v>
+      </c>
+      <c r="L24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" t="s">
+        <v>138</v>
+      </c>
+      <c r="L25" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26" t="s">
+        <v>139</v>
+      </c>
+      <c r="L26" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" t="s">
+        <v>110</v>
+      </c>
+      <c r="F27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L27" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" t="s">
+        <v>141</v>
+      </c>
+      <c r="L28" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" t="s">
+        <v>81</v>
+      </c>
+      <c r="E29" t="s">
+        <v>109</v>
+      </c>
+      <c r="F29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L29" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" t="s">
-        <v>88</v>
-      </c>
-      <c r="K6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" t="s">
-        <v>89</v>
-      </c>
-      <c r="K7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" t="s">
-        <v>90</v>
-      </c>
-      <c r="K8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" t="s">
-        <v>91</v>
-      </c>
-      <c r="K9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" t="s">
-        <v>92</v>
-      </c>
-      <c r="K10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" t="s">
-        <v>94</v>
-      </c>
-      <c r="K12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" t="s">
-        <v>95</v>
-      </c>
-      <c r="K13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" t="s">
-        <v>96</v>
-      </c>
-      <c r="K14" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" t="s">
-        <v>97</v>
-      </c>
-      <c r="K15" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" t="s">
-        <v>98</v>
-      </c>
-      <c r="K16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" t="s">
-        <v>99</v>
-      </c>
-      <c r="K17" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" t="s">
-        <v>100</v>
-      </c>
-      <c r="K18" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" t="s">
-        <v>101</v>
-      </c>
-      <c r="K19" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" t="s">
-        <v>102</v>
-      </c>
-      <c r="K20" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" t="s">
-        <v>103</v>
-      </c>
-      <c r="K21" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" t="s">
-        <v>104</v>
-      </c>
-      <c r="K22" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" t="s">
-        <v>105</v>
-      </c>
-      <c r="K23" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24" t="s">
-        <v>106</v>
-      </c>
-      <c r="K24" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" t="s">
-        <v>107</v>
-      </c>
-      <c r="K25" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" t="s">
-        <v>108</v>
-      </c>
-      <c r="K26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E27" t="s">
-        <v>109</v>
-      </c>
-      <c r="K27" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" t="s">
-        <v>110</v>
-      </c>
-      <c r="K28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" t="s">
-        <v>80</v>
-      </c>
-      <c r="E29" t="s">
-        <v>111</v>
-      </c>
-      <c r="K29" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" t="s">
-        <v>17</v>
-      </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E30" t="s">
         <v>112</v>
       </c>
-      <c r="K30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="F30" t="s">
+        <v>143</v>
+      </c>
+      <c r="L30" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E31" t="s">
         <v>113</v>
       </c>
-      <c r="K31" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="F31" t="s">
+        <v>144</v>
+      </c>
+      <c r="L31" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E32" t="s">
         <v>114</v>
       </c>
-      <c r="K32" t="s">
-        <v>144</v>
+      <c r="F32" t="s">
+        <v>145</v>
+      </c>
+      <c r="L32" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/data/courses_data.xlsx
+++ b/data/courses_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="212">
   <si>
     <t>program</t>
   </si>
@@ -58,15 +58,18 @@
     <t>prerequisite_course</t>
   </si>
   <si>
+    <t>real_link</t>
+  </si>
+  <si>
+    <t>Fullstack Web</t>
+  </si>
+  <si>
+    <t>Cyber Security</t>
+  </si>
+  <si>
     <t>Data Programs</t>
   </si>
   <si>
-    <t>Fullstack Web</t>
-  </si>
-  <si>
-    <t>Cyber Security</t>
-  </si>
-  <si>
     <t>AI-ML</t>
   </si>
   <si>
@@ -76,485 +79,597 @@
     <t>Python</t>
   </si>
   <si>
+    <t>Java</t>
+  </si>
+  <si>
     <t>MERNSTACK</t>
   </si>
   <si>
-    <t>Web</t>
-  </si>
-  <si>
-    <t>Java</t>
+    <t>Cyber Security &amp; Ethical Hacking</t>
+  </si>
+  <si>
+    <t>Data Analytics</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence with Gen AI</t>
+  </si>
+  <si>
+    <t>AI Engineering, MLOps &amp; Development</t>
+  </si>
+  <si>
+    <t>AI, IoT &amp; Intelligent Systems</t>
+  </si>
+  <si>
+    <t>DevOps &amp; Cloud</t>
+  </si>
+  <si>
+    <t>Full Stack Python</t>
+  </si>
+  <si>
+    <t>Advanced Full Stack Python</t>
+  </si>
+  <si>
+    <t>Full Stack Web + Mobile App</t>
+  </si>
+  <si>
+    <t>Fullstack Python with AI</t>
   </si>
   <si>
     <t>Full Stack Data Science With AI</t>
   </si>
   <si>
-    <t>Full Stack Python Web Mobile App</t>
-  </si>
-  <si>
-    <t>Advanced MERN Stack Web Mobile</t>
-  </si>
-  <si>
-    <t>Advance Certification In Data Analytics</t>
-  </si>
-  <si>
-    <t>Full Stack Data Science Gen AI</t>
-  </si>
-  <si>
-    <t>Full Stack Gen AI</t>
+    <t>Fullstack(Web+Mob) Data Science with AI</t>
+  </si>
+  <si>
+    <t>Fullstack Java</t>
   </si>
   <si>
     <t>Advanced Fullstack Java</t>
   </si>
   <si>
-    <t>Advanced MERN Stack</t>
-  </si>
-  <si>
-    <t>Full Stack Java Web Mobile App</t>
-  </si>
-  <si>
-    <t>Fullstack Java</t>
-  </si>
-  <si>
-    <t>MERN Stack</t>
-  </si>
-  <si>
-    <t>Advanced Full Stack Certification</t>
-  </si>
-  <si>
-    <t>Full Stack Python</t>
+    <t>Fullstack Web +Mob App (Java + Flutter)</t>
+  </si>
+  <si>
+    <t>MERNSTACK Development</t>
+  </si>
+  <si>
+    <t>Advance Certification in MERNSTACK</t>
+  </si>
+  <si>
+    <t>MERN Web +Mob App (With React Native)</t>
+  </si>
+  <si>
+    <t>Cyber Security Foundation Track</t>
+  </si>
+  <si>
+    <t>Cyber Security Enterprise Track</t>
   </si>
   <si>
     <t>Cyber Security Advanced Track</t>
   </si>
   <si>
-    <t>Cyber Security Enterprise Track</t>
-  </si>
-  <si>
-    <t>Cyber Security Foundation Track</t>
-  </si>
-  <si>
-    <t>Ultimate AI Super Engineer</t>
-  </si>
-  <si>
-    <t>GenAI AI ML Vibe Coding</t>
-  </si>
-  <si>
-    <t>AI IoT Program</t>
-  </si>
-  <si>
-    <t>GenAI Agentic AI Development</t>
-  </si>
-  <si>
-    <t>Advanced GenAI Mlops</t>
-  </si>
-  <si>
-    <t>AI ML GenAI Agentic AI Mlops IoT</t>
-  </si>
-  <si>
-    <t>Advanced AI Software Engineer</t>
-  </si>
-  <si>
-    <t>Full Stack GenAI Agentic AI IoT</t>
-  </si>
-  <si>
-    <t>Data Analytics For Masters</t>
-  </si>
-  <si>
     <t>Data Analytics Essentials</t>
   </si>
   <si>
     <t>Professional Data Analytics</t>
   </si>
   <si>
-    <t>Data Analytics For Digital Business</t>
-  </si>
-  <si>
-    <t>Digital Marketing Mastery Pro</t>
-  </si>
-  <si>
-    <t>Digital Marketing Executive</t>
-  </si>
-  <si>
-    <t>Advanced Digital Marketing Performance</t>
+    <t>Data Analytics for Digital Business</t>
+  </si>
+  <si>
+    <t>Data Analytics Master</t>
+  </si>
+  <si>
+    <t>GenAI + AI/ML + Vibe Coding Program</t>
+  </si>
+  <si>
+    <t>GenAI + Agentic AI Development Program</t>
+  </si>
+  <si>
+    <t>Full Stack + GenAI + Agentic AI + IoT</t>
+  </si>
+  <si>
+    <t>Advanced GenAI &amp; MLOPS Development Program</t>
+  </si>
+  <si>
+    <t>AI Software Engineer Program</t>
+  </si>
+  <si>
+    <t>AI + IoT Program</t>
+  </si>
+  <si>
+    <t>AI/ML + GenAI + Agentic AI + MLOPS + IoT Program</t>
+  </si>
+  <si>
+    <t>Ultimate AI Super Engineer Program</t>
+  </si>
+  <si>
+    <t>Digital Marketing Executive Program</t>
+  </si>
+  <si>
+    <t>Advanced Digital Marketing &amp; Performance Marketing Program</t>
+  </si>
+  <si>
+    <t>Digital Marketing Mastery Pro – AI-Powered Growth Program</t>
+  </si>
+  <si>
+    <t>Devops &amp; Cloud Computing</t>
+  </si>
+  <si>
+    <t>Covers Figma, HTML, CSS, JavaScript, Backend (Core &amp; Advance Python), Frontend Library (React. JS), Framework (Django with REST (DRF) API), building practical, job-ready skills in Full Stack Python.</t>
+  </si>
+  <si>
+    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Backend (Core &amp; Advance Python), Frontend Library (React. JS), Framework (Django with REST (DRF) API), building practical, job-ready skills in Advanced Full Stack Python.</t>
+  </si>
+  <si>
+    <t>Covers Figma, HTML, CSS, JavaScript, Backend (Core &amp; Advance Python), Frontend Library (React. JS), Framework (Django with REST (DRF) API), Git &amp; SDLC, plus 2 more modules, building practical, job-ready skills in Full Stack Web + Mobile App.</t>
+  </si>
+  <si>
+    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Backend (Core &amp; Advance Python), Frontend Library (React. JS), Framework (Django with REST (DRF) API), Git &amp; SDLC, plus 3 more modules, building practical, job-ready skills in Fullstack Python with AI.</t>
   </si>
   <si>
     <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Backend (Core &amp; Advance Python), Frontend Library (React. JS), Framework (Django with REST (DRF) API), Git &amp; SDLC, plus 7 more modules, building practical, job-ready skills in Full Stack Data Science With AI.</t>
   </si>
   <si>
-    <t>Covers Figma, HTML, CSS, JavaScript, Backend (Core &amp; Advance Python), Frontend Library (React. JS), Framework (Django with REST (DRF) API), Git &amp; SDLC, plus 2 more modules, building practical, job-ready skills in Full Stack Python Web Mobile App.</t>
-  </si>
-  <si>
-    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Database (Mongo DB), Frontend Library (React. JS), Framework (Node js with REST API), Git &amp; SDLC, plus 1 more modules, building practical, job-ready skills in Advanced MERN Stack Web Mobile.</t>
-  </si>
-  <si>
-    <t>Covers Adv Excel with Dashboard, Statistics &amp; Mathematics for Data Analytics, building practical, job-ready skills in Advance Certification In Data Analytics.</t>
-  </si>
-  <si>
-    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Backend (Core &amp; Advance Python), Frontend Library (React. JS), Framework (Django with REST (DRF) API), Git &amp; SDLC, plus 8 more modules, building practical, job-ready skills in Full Stack Data Science Gen AI.</t>
-  </si>
-  <si>
-    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Backend (Core &amp; Advance Python), Frontend Library (React. JS), Framework (Django with REST (DRF) API), Git &amp; SDLC, plus 3 more modules, building practical, job-ready skills in Full Stack Gen AI.</t>
+    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Backend (Core &amp; Advance Python), Frontend Library (React. JS), Framework (Django with REST (DRF) API), Git &amp; SDLC, plus 8 more modules, building practical, job-ready skills in Fullstack(Web+Mob) Data Science with AI.</t>
+  </si>
+  <si>
+    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Backend (Core &amp; Advance Java), Framework (Springboot with CRUD), Data Structures &amp; Algorithms (with Java), building practical, job-ready skills in Fullstack Java.</t>
   </si>
   <si>
     <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Backend (Core &amp; Advance Java), Frontend Library (React. JS), Framework (Springboot), Git &amp; SDLC, plus 1 more modules, building practical, job-ready skills in Advanced Fullstack Java.</t>
   </si>
   <si>
-    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Database (Mongo DB), Frontend Library (React. JS), Framework (Node js with REST API), Git &amp; SDLC, building practical, job-ready skills in Advanced MERN Stack.</t>
-  </si>
-  <si>
-    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Backend (Core &amp; Advance Java), Frontend Library (React. JS), Framework (Springboot with API), Git &amp; SDLC, plus 2 more modules, building practical, job-ready skills in Full Stack Java Web Mobile App.</t>
-  </si>
-  <si>
-    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Backend (Core &amp; Advance Java), Framework (Springboot with CRUD), Data Structures &amp; Algorithms (with Java), building practical, job-ready skills in Fullstack Java.</t>
-  </si>
-  <si>
-    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Database (Mongo DB), Frontend Library (React. JS), Framework (Node js with REST API), building practical, job-ready skills in MERN Stack.</t>
-  </si>
-  <si>
-    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Backend (Core &amp; Advance Python), Frontend Library (React. JS), Framework (Django with REST (DRF) API), building practical, job-ready skills in Advanced Full Stack Certification.</t>
-  </si>
-  <si>
-    <t>Covers Figma, HTML, CSS, JavaScript, Backend (Core &amp; Advance Python), Frontend Library (React. JS), Framework (Django with REST (DRF) API), building practical, job-ready skills in Full Stack Python.</t>
+    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Backend (Core &amp; Advance Java), Frontend Library (React. JS), Framework (Springboot with API), Git &amp; SDLC, plus 2 more modules, building practical, job-ready skills in Fullstack Web +Mob App (Java + Flutter).</t>
+  </si>
+  <si>
+    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Database (Mongo DB), Frontend Library (React. JS), Framework (Node js with REST API), building practical, job-ready skills in MERNSTACK Development.</t>
+  </si>
+  <si>
+    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Database (Mongo DB), Frontend Library (React. JS), Framework (Node js with REST API), Git &amp; SDLC, building practical, job-ready skills in Advance Certification in MERNSTACK.</t>
+  </si>
+  <si>
+    <t>Covers Frontend (Figma, HTML, CSS, JavaScript), Database (Mongo DB), Frontend Library (React. JS), Framework (Node js with REST API), Git &amp; SDLC, plus 1 more modules, building practical, job-ready skills in MERN Web +Mob App (With React Native).</t>
+  </si>
+  <si>
+    <t>Covers Foundation, Security Essentials, Ethical Hacking Methodology, Web Application Security, Security Operations &amp; Incident Response, building practical, job-ready skills in Cyber Security Foundation Track.</t>
+  </si>
+  <si>
+    <t>Covers Foundation, Security Essentials, Ethical Hacking Methodology, Web Application Security, Security Operations &amp; Incident Response, plus 5 more modules, building practical, job-ready skills in Cyber Security Enterprise Track.</t>
   </si>
   <si>
     <t>Covers Foundation, Security Essentials, Ethical Hacking Methodology, Web Application Security, Security Operations &amp; Incident Response, plus 10 more modules, building practical, job-ready skills in Cyber Security Advanced Track.</t>
   </si>
   <si>
-    <t>Covers Foundation, Security Essentials, Ethical Hacking Methodology, Web Application Security, Security Operations &amp; Incident Response, plus 5 more modules, building practical, job-ready skills in Cyber Security Enterprise Track.</t>
-  </si>
-  <si>
-    <t>Covers Foundation, Security Essentials, Ethical Hacking Methodology, Web Application Security, Security Operations &amp; Incident Response, building practical, job-ready skills in Cyber Security Foundation Track.</t>
-  </si>
-  <si>
-    <t>Covers Python Fundamentals, Data Structures &amp; Data Fundamentals, Machine Learning Foundations, Data Analytics &amp; Visualization, Computer Vision, plus 18 more modules, building practical, job-ready skills in Ultimate AI Super Engineer.</t>
-  </si>
-  <si>
-    <t>Covers Python Fundamentals, Machine Learning Foundations, GenAI Foundations, Vibe Coding / AI-Assisted Development, AI Product Development, building practical, job-ready skills in GenAI AI ML Vibe Coding.</t>
-  </si>
-  <si>
-    <t>Covers Python Fundamentals, Machine Learning Foundations, Computer Vision, IoT &amp; Embedded Systems, AI + IoT Integration, building practical, job-ready skills in AI IoT Program.</t>
-  </si>
-  <si>
-    <t>Covers Python Fundamentals, AI/ML Foundations &amp; Deep Learning, GenAI Foundations, LLM Application Development, RAG, plus 3 more modules, building practical, job-ready skills in GenAI Agentic AI Development.</t>
-  </si>
-  <si>
-    <t>Covers Python Fundamentals, Data Structures &amp; Data Fundamentals, Data Analytics &amp; Visualization, GenAI Foundations, Vibe Coding / AI-Assisted Development, plus 5 more modules, building practical, job-ready skills in Advanced GenAI Mlops.</t>
-  </si>
-  <si>
-    <t>Covers Python Fundamentals, Data Structures &amp; Data Fundamentals, Machine Learning Foundations, Data Analytics &amp; Visualization, AI/ML Foundations &amp; Deep Learning, plus 8 more modules, building practical, job-ready skills in AI ML GenAI Agentic AI Mlops IoT.</t>
-  </si>
-  <si>
-    <t>Covers Full-Stack Development, AI Product Development, AI Engineering, Robotics &amp; Smart Systems, Deployment &amp; Production, plus 1 more modules, building practical, job-ready skills in Advanced AI Software Engineer.</t>
-  </si>
-  <si>
-    <t>Covers GenAI Foundations, LLM Application Development, RAG, AI Agents, Advanced Agentic AI, plus 3 more modules, building practical, job-ready skills in Full Stack GenAI Agentic AI IoT.</t>
-  </si>
-  <si>
-    <t>Covers Data Analytics Foundations, Advanced Excel, Statistics for Data Analytics, Python Programming for Analytics, NumPy &amp; Pandas, plus 11 more modules, building practical, job-ready skills in Data Analytics For Masters.</t>
-  </si>
-  <si>
     <t>Covers Data Analytics Foundations, Advanced Excel, Statistics for Data Analytics, Python Programming for Analytics, Power BI &amp; Business Intelligence, building practical, job-ready skills in Data Analytics Essentials.</t>
   </si>
   <si>
     <t>Covers Data Analytics Foundations, Advanced Excel, Statistics for Data Analytics, Python Programming for Analytics, NumPy &amp; Pandas, plus 5 more modules, building practical, job-ready skills in Professional Data Analytics.</t>
   </si>
   <si>
-    <t>Covers Data Analytics Foundations, Advanced Excel, Statistics for Data Analytics, Python Programming for Analytics, NumPy &amp; Pandas, plus 11 more modules, building practical, job-ready skills in Data Analytics For Digital Business.</t>
-  </si>
-  <si>
-    <t>Covers Digital Marketing Foundations &amp; Strategy, SEO Specialist Track, Website Development &amp; Landing Pages, Social Media Marketing &amp; Management, Content Marketing &amp; Copywriting, plus 10 more modules, building practical, job-ready skills in Digital Marketing Mastery Pro.</t>
-  </si>
-  <si>
-    <t>Covers Digital Marketing Foundations &amp; Strategy, SEO Specialist Track, Website Development &amp; Landing Pages, Social Media Marketing &amp; Management, Content Marketing &amp; Copywriting, plus 3 more modules, building practical, job-ready skills in Digital Marketing Executive.</t>
-  </si>
-  <si>
-    <t>Covers Digital Marketing Foundations &amp; Strategy, SEO Specialist Track, Website Development &amp; Landing Pages, Social Media Marketing &amp; Management, Content Marketing &amp; Copywriting, plus 7 more modules, building practical, job-ready skills in Advanced Digital Marketing Performance.</t>
+    <t>Covers Data Analytics Foundations, Advanced Excel, Statistics for Data Analytics, Python Programming for Analytics, NumPy &amp; Pandas, plus 11 more modules, building practical, job-ready skills in Data Analytics for Digital Business.</t>
+  </si>
+  <si>
+    <t>Covers Data Analytics Foundations, Advanced Excel, Statistics for Data Analytics, Python Programming for Analytics, NumPy &amp; Pandas, plus 11 more modules, building practical, job-ready skills in Data Analytics Master.</t>
+  </si>
+  <si>
+    <t>Covers Python Fundamentals, Machine Learning Foundations, GenAI Foundations, Vibe Coding / AI-Assisted Development, AI Product Development, building practical, job-ready skills in GenAI + AI/ML + Vibe Coding Program.</t>
+  </si>
+  <si>
+    <t>Covers Python Fundamentals, AI/ML Foundations &amp; Deep Learning, GenAI Foundations, LLM Application Development, RAG, plus 3 more modules, building practical, job-ready skills in GenAI + Agentic AI Development Program.</t>
+  </si>
+  <si>
+    <t>Covers GenAI Foundations, LLM Application Development, RAG, AI Agents, Advanced Agentic AI, plus 3 more modules, building practical, job-ready skills in Full Stack + GenAI + Agentic AI + IoT.</t>
+  </si>
+  <si>
+    <t>Covers Python Fundamentals, Data Structures &amp; Data Fundamentals, Data Analytics &amp; Visualization, GenAI Foundations, Vibe Coding / AI-Assisted Development, plus 5 more modules, building practical, job-ready skills in Advanced GenAI &amp; MLOPS Development Program.</t>
+  </si>
+  <si>
+    <t>Covers Full-Stack Development, AI Product Development, AI Engineering, Robotics &amp; Smart Systems, Deployment &amp; Production, plus 1 more modules, building practical, job-ready skills in AI Software Engineer Program.</t>
+  </si>
+  <si>
+    <t>Covers Python Fundamentals, Machine Learning Foundations, Computer Vision, IoT &amp; Embedded Systems, AI + IoT Integration, building practical, job-ready skills in AI + IoT Program.</t>
+  </si>
+  <si>
+    <t>Covers Python Fundamentals, Data Structures &amp; Data Fundamentals, Machine Learning Foundations, Data Analytics &amp; Visualization, AI/ML Foundations &amp; Deep Learning, plus 8 more modules, building practical, job-ready skills in AI/ML + GenAI + Agentic AI + MLOPS + IoT Program.</t>
+  </si>
+  <si>
+    <t>Covers Python Fundamentals, Data Structures &amp; Data Fundamentals, Machine Learning Foundations, Data Analytics &amp; Visualization, Computer Vision, plus 18 more modules, building practical, job-ready skills in Ultimate AI Super Engineer Program.</t>
+  </si>
+  <si>
+    <t>Covers Digital Marketing Foundations &amp; Strategy, SEO Specialist Track, Website Development &amp; Landing Pages, Social Media Marketing &amp; Management, Content Marketing &amp; Copywriting, plus 3 more modules, building practical, job-ready skills in Digital Marketing Executive Program.</t>
+  </si>
+  <si>
+    <t>Covers Digital Marketing Foundations &amp; Strategy, SEO Specialist Track, Website Development &amp; Landing Pages, Social Media Marketing &amp; Management, Content Marketing &amp; Copywriting, plus 7 more modules, building practical, job-ready skills in Advanced Digital Marketing &amp; Performance Marketing Program.</t>
+  </si>
+  <si>
+    <t>Covers Digital Marketing Foundations &amp; Strategy, SEO Specialist Track, Website Development &amp; Landing Pages, Social Media Marketing &amp; Management, Content Marketing &amp; Copywriting, plus 10 more modules, building practical, job-ready skills in Digital Marketing Mastery Pro – AI-Powered Growth Program.</t>
+  </si>
+  <si>
+    <t>Devops &amp; Cloud Computing — full curriculum details not yet provided by the institute.</t>
+  </si>
+  <si>
+    <t>Figma, HTML, CSS, JavaScript; Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API)</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API)</t>
+  </si>
+  <si>
+    <t>Figma, HTML, CSS, JavaScript; Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API); Git &amp; SDLC; Data Structures &amp; Algorithms (Python); Mobile App (Flutter)</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API); Git &amp; SDLC; Data Structures &amp; Algorithms (Python); Machine Learning (Supervised &amp; Unsupervised); Artificial Intelligence</t>
   </si>
   <si>
     <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API); Git &amp; SDLC; Data Structures &amp; Algorithms (Python); Machine Learning (Supervised &amp; Unsupervised); Artificial Intelligence; Database (MySQL); Python Libraries(Numpy, Pandas, Matplotlib, Seaborn); Data Visualization (Power BI); Cloud (Azure)</t>
   </si>
   <si>
-    <t>Figma, HTML, CSS, JavaScript; Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API); Git &amp; SDLC; Data Structures &amp; Algorithms (Python); Mobile App (Flutter)</t>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API); Git &amp; SDLC; Data Structures &amp; Algorithms (Python); Machine Learning (Supervised &amp; Unsupervised); Artificial Intelligence; Database (MySQL); Python Libraries(Numpy, Pandas, Matplotlib, Seaborn); Data Visualization (Power BI); Cloud (Azure); Mobile App (Flutter)</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Java); Framework (Springboot with CRUD); Data Structures &amp; Algorithms (with Java)</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Java); Frontend Library (React. JS); Framework (Springboot); Git &amp; SDLC; Data Structures &amp; Algorithms (Python)</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Java); Frontend Library (React. JS); Framework (Springboot with API); Git &amp; SDLC; Data Structures &amp; Algorithms (Python); Mobile App (Flutter)</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Database (Mongo DB); Frontend Library (React. JS); Framework (Node js with REST API)</t>
+  </si>
+  <si>
+    <t>Frontend (Figma, HTML, CSS, JavaScript); Database (Mongo DB); Frontend Library (React. JS); Framework (Node js with REST API); Git &amp; SDLC</t>
   </si>
   <si>
     <t>Frontend (Figma, HTML, CSS, JavaScript); Database (Mongo DB); Frontend Library (React. JS); Framework (Node js with REST API); Git &amp; SDLC; Mobile App (React Native)</t>
   </si>
   <si>
-    <t>Adv Excel with Dashboard; Statistics &amp; Mathematics for Data Analytics</t>
-  </si>
-  <si>
-    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API); Git &amp; SDLC; Data Structures &amp; Algorithms (Python); Machine Learning (Supervised &amp; Unsupervised); Artificial Intelligence; Database (MySQL); Python Libraries(Numpy, Pandas, Matplotlib, Seaborn); Data Visualization (Power BI); Cloud (Azure); Mobile App (Flutter)</t>
-  </si>
-  <si>
-    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API); Git &amp; SDLC; Data Structures &amp; Algorithms (Python); Machine Learning (Supervised &amp; Unsupervised); Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Java); Frontend Library (React. JS); Framework (Springboot); Git &amp; SDLC; Data Structures &amp; Algorithms (Python)</t>
-  </si>
-  <si>
-    <t>Frontend (Figma, HTML, CSS, JavaScript); Database (Mongo DB); Frontend Library (React. JS); Framework (Node js with REST API); Git &amp; SDLC</t>
-  </si>
-  <si>
-    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Java); Frontend Library (React. JS); Framework (Springboot with API); Git &amp; SDLC; Data Structures &amp; Algorithms (Python); Mobile App (Flutter)</t>
-  </si>
-  <si>
-    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Java); Framework (Springboot with CRUD); Data Structures &amp; Algorithms (with Java)</t>
-  </si>
-  <si>
-    <t>Frontend (Figma, HTML, CSS, JavaScript); Database (Mongo DB); Frontend Library (React. JS); Framework (Node js with REST API)</t>
-  </si>
-  <si>
-    <t>Frontend (Figma, HTML, CSS, JavaScript); Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API)</t>
-  </si>
-  <si>
-    <t>Figma, HTML, CSS, JavaScript; Backend (Core &amp; Advance Python); Frontend Library (React. JS); Framework (Django with REST (DRF) API)</t>
+    <t>Foundation; Security Essentials; Ethical Hacking Methodology; Web Application Security; Security Operations &amp; Incident Response</t>
+  </si>
+  <si>
+    <t>Foundation; Security Essentials; Ethical Hacking Methodology; Web Application Security; Security Operations &amp; Incident Response; AWS Solution Architect — Security Focus; Advanced VAPT; Mobile &amp; Digital Forensics; Red Team Operations; Bug Bounty &amp; Hacker Mindset</t>
   </si>
   <si>
     <t>Foundation; Security Essentials; Ethical Hacking Methodology; Web Application Security; Security Operations &amp; Incident Response; AWS Solution Architect — Security Focus; Advanced VAPT; Mobile &amp; Digital Forensics; Red Team Operations; Bug Bounty &amp; Hacker Mindset; Build Modern Infrastructure; Automate the Platform; AI Foundations for Security Professionals; Generative AI in Practice; AI Agents &amp; AI Security</t>
   </si>
   <si>
-    <t>Foundation; Security Essentials; Ethical Hacking Methodology; Web Application Security; Security Operations &amp; Incident Response; AWS Solution Architect — Security Focus; Advanced VAPT; Mobile &amp; Digital Forensics; Red Team Operations; Bug Bounty &amp; Hacker Mindset</t>
-  </si>
-  <si>
-    <t>Foundation; Security Essentials; Ethical Hacking Methodology; Web Application Security; Security Operations &amp; Incident Response</t>
+    <t>Data Analytics Foundations; Advanced Excel; Statistics for Data Analytics; Python Programming for Analytics; Power BI &amp; Business Intelligence</t>
+  </si>
+  <si>
+    <t>Data Analytics Foundations; Advanced Excel; Statistics for Data Analytics; Python Programming for Analytics; NumPy &amp; Pandas; Data Visualization with Python; SQL &amp; Database Analytics; Power BI &amp; Business Intelligence; Exploratory Data Analysis (EDA); ETL &amp; Data Preparation</t>
+  </si>
+  <si>
+    <t>Data Analytics Foundations; Advanced Excel; Statistics for Data Analytics; Python Programming for Analytics; NumPy &amp; Pandas; Data Visualization with Python; SQL &amp; Database Analytics; Power BI &amp; Business Intelligence; Exploratory Data Analysis (EDA); ETL &amp; Data Preparation; Digital Business Analytics; Digital Marketing Analytics; GenAI Tools for Data Analytics; Graphics &amp; Video for Digital Analytics; Advanced Analytics Projects; Industry Internship / Capstone</t>
+  </si>
+  <si>
+    <t>Python Fundamentals; Machine Learning Foundations; GenAI Foundations; Vibe Coding / AI-Assisted Development; AI Product Development</t>
+  </si>
+  <si>
+    <t>Python Fundamentals; AI/ML Foundations &amp; Deep Learning; GenAI Foundations; LLM Application Development; RAG; AI Agents; Advanced Agentic AI; AWS / Cloud</t>
+  </si>
+  <si>
+    <t>GenAI Foundations; LLM Application Development; RAG; AI Agents; Advanced Agentic AI; IoT &amp; Embedded Systems; AI + IoT Integration; Full-Stack Development</t>
+  </si>
+  <si>
+    <t>Python Fundamentals; Data Structures &amp; Data Fundamentals; Data Analytics &amp; Visualization; GenAI Foundations; Vibe Coding / AI-Assisted Development; LLM Application Development; RAG; AI Agents; MLOps / AIOps; SQL &amp; Database Management</t>
+  </si>
+  <si>
+    <t>Full-Stack Development; AI Product Development; AI Engineering; Robotics &amp; Smart Systems; Deployment &amp; Production; Capstone &amp; Industry Project</t>
+  </si>
+  <si>
+    <t>Python Fundamentals; Machine Learning Foundations; Computer Vision; IoT &amp; Embedded Systems; AI + IoT Integration</t>
+  </si>
+  <si>
+    <t>Python Fundamentals; Data Structures &amp; Data Fundamentals; Machine Learning Foundations; Data Analytics &amp; Visualization; AI/ML Foundations &amp; Deep Learning; GenAI Foundations; LLM Application Development; RAG; AI Agents; MLOps / AIOps; AWS / Cloud; IoT &amp; Embedded Systems; AI + IoT Integration</t>
   </si>
   <si>
     <t>Python Fundamentals; Data Structures &amp; Data Fundamentals; Machine Learning Foundations; Data Analytics &amp; Visualization; Computer Vision; AI/ML Foundations &amp; Deep Learning; GenAI Foundations; Vibe Coding / AI-Assisted Development; LLM Application Development; RAG; AI Agents; Advanced Agentic AI; MLOps / AIOps; SQL &amp; Database Management; AWS / Cloud; IoT &amp; Embedded Systems; AI + IoT Integration; Full-Stack Development; AI Product Development; AI Engineering; Robotics &amp; Smart Systems; Deployment &amp; Production; Capstone &amp; Industry Project</t>
   </si>
   <si>
-    <t>Python Fundamentals; Machine Learning Foundations; GenAI Foundations; Vibe Coding / AI-Assisted Development; AI Product Development</t>
-  </si>
-  <si>
-    <t>Python Fundamentals; Machine Learning Foundations; Computer Vision; IoT &amp; Embedded Systems; AI + IoT Integration</t>
-  </si>
-  <si>
-    <t>Python Fundamentals; AI/ML Foundations &amp; Deep Learning; GenAI Foundations; LLM Application Development; RAG; AI Agents; Advanced Agentic AI; AWS / Cloud</t>
-  </si>
-  <si>
-    <t>Python Fundamentals; Data Structures &amp; Data Fundamentals; Data Analytics &amp; Visualization; GenAI Foundations; Vibe Coding / AI-Assisted Development; LLM Application Development; RAG; AI Agents; MLOps / AIOps; SQL &amp; Database Management</t>
-  </si>
-  <si>
-    <t>Python Fundamentals; Data Structures &amp; Data Fundamentals; Machine Learning Foundations; Data Analytics &amp; Visualization; AI/ML Foundations &amp; Deep Learning; GenAI Foundations; LLM Application Development; RAG; AI Agents; MLOps / AIOps; AWS / Cloud; IoT &amp; Embedded Systems; AI + IoT Integration</t>
-  </si>
-  <si>
-    <t>Full-Stack Development; AI Product Development; AI Engineering; Robotics &amp; Smart Systems; Deployment &amp; Production; Capstone &amp; Industry Project</t>
-  </si>
-  <si>
-    <t>GenAI Foundations; LLM Application Development; RAG; AI Agents; Advanced Agentic AI; IoT &amp; Embedded Systems; AI + IoT Integration; Full-Stack Development</t>
-  </si>
-  <si>
-    <t>Data Analytics Foundations; Advanced Excel; Statistics for Data Analytics; Python Programming for Analytics; NumPy &amp; Pandas; Data Visualization with Python; SQL &amp; Database Analytics; Power BI &amp; Business Intelligence; Exploratory Data Analysis (EDA); ETL &amp; Data Preparation; Digital Business Analytics; Digital Marketing Analytics; GenAI Tools for Data Analytics; Graphics &amp; Video for Digital Analytics; Advanced Analytics Projects; Industry Internship / Capstone</t>
-  </si>
-  <si>
-    <t>Data Analytics Foundations; Advanced Excel; Statistics for Data Analytics; Python Programming for Analytics; Power BI &amp; Business Intelligence</t>
-  </si>
-  <si>
-    <t>Data Analytics Foundations; Advanced Excel; Statistics for Data Analytics; Python Programming for Analytics; NumPy &amp; Pandas; Data Visualization with Python; SQL &amp; Database Analytics; Power BI &amp; Business Intelligence; Exploratory Data Analysis (EDA); ETL &amp; Data Preparation</t>
+    <t>Digital Marketing Foundations &amp; Strategy; SEO Specialist Track; Website Development &amp; Landing Pages; Social Media Marketing &amp; Management; Content Marketing &amp; Copywriting; Lead Generation, Landing Pages &amp; Conversion; Search Engine Marketing (SEM) &amp; Paid Search; Online Display &amp; Remarketing</t>
+  </si>
+  <si>
+    <t>Digital Marketing Foundations &amp; Strategy; SEO Specialist Track; Website Development &amp; Landing Pages; Social Media Marketing &amp; Management; Content Marketing &amp; Copywriting; Lead Generation, Landing Pages &amp; Conversion; Search Engine Marketing (SEM) &amp; Paid Search; Online Display &amp; Remarketing; E-Commerce &amp; Online Sales Marketing; Video Marketing &amp; YouTube; Mobile App Marketing; Google Ads Ecosystem: Discovery, Performance Max &amp; Search</t>
   </si>
   <si>
     <t>Digital Marketing Foundations &amp; Strategy; SEO Specialist Track; Website Development &amp; Landing Pages; Social Media Marketing &amp; Management; Content Marketing &amp; Copywriting; Lead Generation, Landing Pages &amp; Conversion; Search Engine Marketing (SEM) &amp; Paid Search; Online Display &amp; Remarketing; E-Commerce &amp; Online Sales Marketing; Video Marketing &amp; YouTube; Mobile App Marketing; Google Ads Ecosystem: Discovery, Performance Max &amp; Search; Growth, Reputation, Email &amp; Messaging; Freelancing, Portfolio, Resume &amp; Interview Readiness; AI-Powered Digital Marketing &amp; Career Growth</t>
   </si>
   <si>
-    <t>Digital Marketing Foundations &amp; Strategy; SEO Specialist Track; Website Development &amp; Landing Pages; Social Media Marketing &amp; Management; Content Marketing &amp; Copywriting; Lead Generation, Landing Pages &amp; Conversion; Search Engine Marketing (SEM) &amp; Paid Search; Online Display &amp; Remarketing</t>
-  </si>
-  <si>
-    <t>Digital Marketing Foundations &amp; Strategy; SEO Specialist Track; Website Development &amp; Landing Pages; Social Media Marketing &amp; Management; Content Marketing &amp; Copywriting; Lead Generation, Landing Pages &amp; Conversion; Search Engine Marketing (SEM) &amp; Paid Search; Online Display &amp; Remarketing; E-Commerce &amp; Online Sales Marketing; Video Marketing &amp; YouTube; Mobile App Marketing; Google Ads Ecosystem: Discovery, Performance Max &amp; Search</t>
+    <t>full-stack-python-course</t>
+  </si>
+  <si>
+    <t>advanced-full-stack-certification-course</t>
+  </si>
+  <si>
+    <t>full-stack-python-web-mobile-app-course</t>
+  </si>
+  <si>
+    <t>full-stack-gen-ai-course</t>
   </si>
   <si>
     <t>full-stack-data-science-with-ai-course</t>
   </si>
   <si>
-    <t>full-stack-python-web-mobile-app-course</t>
+    <t>full-stack-data-science-gen-ai-course</t>
+  </si>
+  <si>
+    <t>fullstack-java-course</t>
+  </si>
+  <si>
+    <t>advanced-fullstack-java-course</t>
+  </si>
+  <si>
+    <t>full-stack-java-web-mobile-app-course</t>
+  </si>
+  <si>
+    <t>mern-stack-course</t>
+  </si>
+  <si>
+    <t>advanced-mern-stack-course</t>
   </si>
   <si>
     <t>advanced-mern-stack-web-mobile-course</t>
   </si>
   <si>
-    <t>advance-certification-in-data-analytics-course</t>
-  </si>
-  <si>
-    <t>full-stack-data-science-gen-ai-course</t>
-  </si>
-  <si>
-    <t>full-stack-gen-ai-course</t>
-  </si>
-  <si>
-    <t>advanced-fullstack-java-course</t>
-  </si>
-  <si>
-    <t>advanced-mern-stack-course</t>
-  </si>
-  <si>
-    <t>full-stack-java-web-mobile-app-course</t>
-  </si>
-  <si>
-    <t>fullstack-java-course</t>
-  </si>
-  <si>
-    <t>mern-stack-course</t>
-  </si>
-  <si>
-    <t>advanced-full-stack-certification-course</t>
-  </si>
-  <si>
-    <t>full-stack-python-course</t>
+    <t>cyber-security-foundation-track</t>
+  </si>
+  <si>
+    <t>cyber-security-enterprise-track</t>
   </si>
   <si>
     <t>cyber-security-advanced-track</t>
   </si>
   <si>
-    <t>cyber-security-enterprise-track</t>
-  </si>
-  <si>
-    <t>cyber-security-foundation-track</t>
+    <t>data-analytics-essentials</t>
+  </si>
+  <si>
+    <t>professional-data-analytics</t>
+  </si>
+  <si>
+    <t>data-analytics-for-digital-business</t>
+  </si>
+  <si>
+    <t>data-analytics-for-masters</t>
+  </si>
+  <si>
+    <t>genai-ai-ml-vibe-coding</t>
+  </si>
+  <si>
+    <t>genai-agentic-ai-development</t>
+  </si>
+  <si>
+    <t>full-stack-genai-agentic-ai-iot</t>
+  </si>
+  <si>
+    <t>advanced-genai-mlops</t>
+  </si>
+  <si>
+    <t>advanced-ai-software-engineer</t>
+  </si>
+  <si>
+    <t>ai-iot-program</t>
+  </si>
+  <si>
+    <t>ai-ml-genai-agentic-ai-mlops-iot</t>
   </si>
   <si>
     <t>ultimate-ai-super-engineer</t>
   </si>
   <si>
-    <t>genai-ai-ml-vibe-coding</t>
-  </si>
-  <si>
-    <t>ai-iot-program</t>
-  </si>
-  <si>
-    <t>genai-agentic-ai-development</t>
-  </si>
-  <si>
-    <t>advanced-genai-mlops</t>
-  </si>
-  <si>
-    <t>ai-ml-genai-agentic-ai-mlops-iot</t>
-  </si>
-  <si>
-    <t>advanced-ai-software-engineer</t>
-  </si>
-  <si>
-    <t>full-stack-genai-agentic-ai-iot</t>
-  </si>
-  <si>
-    <t>data-analytics-for-masters</t>
-  </si>
-  <si>
-    <t>data-analytics-essentials</t>
-  </si>
-  <si>
-    <t>professional-data-analytics</t>
-  </si>
-  <si>
-    <t>data-analytics-for-digital-business</t>
+    <t>digital-marketing-executive</t>
+  </si>
+  <si>
+    <t>advanced-digital-marketing-performance</t>
   </si>
   <si>
     <t>digital-marketing-mastery-pro</t>
   </si>
   <si>
-    <t>digital-marketing-executive</t>
-  </si>
-  <si>
-    <t>advanced-digital-marketing-performance</t>
+    <t>cloud-devops-course</t>
+  </si>
+  <si>
+    <t>backend, core, django with rest drf, figma html css javascript, framework, frontend library, python, react js</t>
+  </si>
+  <si>
+    <t>backend, core, css, django with rest drf, figma, framework, frontend, frontend library, html, javascript, python, react js</t>
+  </si>
+  <si>
+    <t>algorithms, backend, core, data structures, django with rest drf, figma html css javascript, flutter, framework, frontend library, git, mobile app, python, react js, sdlc</t>
+  </si>
+  <si>
+    <t>algorithms, artificial intelligence, backend, core, css, data structures, django with rest drf, figma, framework, frontend, frontend library, git, html, javascript, machine learning, python, react js, sdlc, supervised, unsupervised</t>
   </si>
   <si>
     <t>algorithms, artificial intelligence, azure, backend, cloud, core, css, data structures, data visualization, database, django with rest drf, figma, framework, frontend, frontend library, git, html, javascript, machine learning, matplotlib, mysql, numpy, pandas, power bi, python, python libraries, react js, sdlc, seaborn, supervised, unsupervised</t>
   </si>
   <si>
-    <t>algorithms, backend, core, data structures, django with rest drf, figma html css javascript, flutter, framework, frontend library, git, mobile app, python, react js, sdlc</t>
+    <t>algorithms, artificial intelligence, azure, backend, cloud, core, css, data structures, data visualization, database, django with rest drf, figma, flutter, framework, frontend, frontend library, git, html, javascript, machine learning, matplotlib, mobile app, mysql, numpy, pandas, power bi, python, python libraries, react js, sdlc, seaborn, supervised, unsupervised</t>
+  </si>
+  <si>
+    <t>algorithms, backend, core, css, data structures, figma, framework, frontend, html, java, javascript, springboot with crud</t>
+  </si>
+  <si>
+    <t>algorithms, backend, core, css, data structures, figma, framework, frontend, frontend library, git, html, java, javascript, python, react js, sdlc, springboot</t>
+  </si>
+  <si>
+    <t>algorithms, backend, core, css, data structures, figma, flutter, framework, frontend, frontend library, git, html, java, javascript, mobile app, python, react js, sdlc, springboot with api</t>
+  </si>
+  <si>
+    <t>css, database, figma, framework, frontend, frontend library, html, javascript, mongo db, node js with rest api, react js</t>
+  </si>
+  <si>
+    <t>css, database, figma, framework, frontend, frontend library, git, html, javascript, mongo db, node js with rest api, react js, sdlc</t>
   </si>
   <si>
     <t>css, database, figma, framework, frontend, frontend library, git, html, javascript, mobile app, mongo db, node js with rest api, react js, react native, sdlc</t>
   </si>
   <si>
-    <t>adv excel with dashboard, mathematics for data analytics, statistics</t>
-  </si>
-  <si>
-    <t>algorithms, artificial intelligence, azure, backend, cloud, core, css, data structures, data visualization, database, django with rest drf, figma, flutter, framework, frontend, frontend library, git, html, javascript, machine learning, matplotlib, mobile app, mysql, numpy, pandas, power bi, python, python libraries, react js, sdlc, seaborn, supervised, unsupervised</t>
-  </si>
-  <si>
-    <t>algorithms, artificial intelligence, backend, core, css, data structures, django with rest drf, figma, framework, frontend, frontend library, git, html, javascript, machine learning, python, react js, sdlc, supervised, unsupervised</t>
-  </si>
-  <si>
-    <t>algorithms, backend, core, css, data structures, figma, framework, frontend, frontend library, git, html, java, javascript, python, react js, sdlc, springboot</t>
-  </si>
-  <si>
-    <t>css, database, figma, framework, frontend, frontend library, git, html, javascript, mongo db, node js with rest api, react js, sdlc</t>
-  </si>
-  <si>
-    <t>algorithms, backend, core, css, data structures, figma, flutter, framework, frontend, frontend library, git, html, java, javascript, mobile app, python, react js, sdlc, springboot with api</t>
-  </si>
-  <si>
-    <t>algorithms, backend, core, css, data structures, figma, framework, frontend, html, java, javascript, springboot with crud</t>
-  </si>
-  <si>
-    <t>css, database, figma, framework, frontend, frontend library, html, javascript, mongo db, node js with rest api, react js</t>
-  </si>
-  <si>
-    <t>backend, core, css, django with rest drf, figma, framework, frontend, frontend library, html, javascript, python, react js</t>
-  </si>
-  <si>
-    <t>backend, core, django with rest drf, figma html css javascript, framework, frontend library, python, react js</t>
+    <t>ethical hacking methodology, foundation, incident response, security essentials, security operations, web application security</t>
+  </si>
+  <si>
+    <t>advanced vapt, aws solution architect  security focus, bug bounty, digital forensics, ethical hacking methodology, foundation, hacker mindset, incident response, mobile, red team operations, security essentials, security operations, web application security</t>
   </si>
   <si>
     <t>advanced vapt, ai agents, ai foundations for security professionals, ai security, automate the platform, aws solution architect  security focus, bug bounty, build modern infrastructure, digital forensics, ethical hacking methodology, foundation, generative ai in practice, hacker mindset, incident response, mobile, red team operations, security essentials, security operations, web application security</t>
   </si>
   <si>
-    <t>advanced vapt, aws solution architect  security focus, bug bounty, digital forensics, ethical hacking methodology, foundation, hacker mindset, incident response, mobile, red team operations, security essentials, security operations, web application security</t>
-  </si>
-  <si>
-    <t>ethical hacking methodology, foundation, incident response, security essentials, security operations, web application security</t>
+    <t>advanced excel, business intelligence, data analytics foundations, power bi, python programming for analytics, statistics for data analytics</t>
+  </si>
+  <si>
+    <t>advanced excel, business intelligence, data analytics foundations, data preparation, data visualization with python, database analytics, eda, etl, exploratory data analysis, numpy, pandas, power bi, python programming for analytics, sql, statistics for data analytics</t>
+  </si>
+  <si>
+    <t>advanced analytics projects, advanced excel, business intelligence, capstone, data analytics foundations, data preparation, data visualization with python, database analytics, digital business analytics, digital marketing analytics, eda, etl, exploratory data analysis, genai tools for data analytics, graphics, industry internship, numpy, pandas, power bi, python programming for analytics, sql, statistics for data analytics, video for digital analytics</t>
+  </si>
+  <si>
+    <t>ai product development, aiassisted development, genai foundations, machine learning foundations, python fundamentals, vibe coding</t>
+  </si>
+  <si>
+    <t>advanced agentic ai, ai agents, aws, cloud, deep learning, genai foundations, llm application development, ml foundations, python fundamentals, rag</t>
+  </si>
+  <si>
+    <t>advanced agentic ai, ai  iot integration, ai agents, embedded systems, fullstack development, genai foundations, iot, llm application development, rag</t>
+  </si>
+  <si>
+    <t>ai agents, aiassisted development, aiops, data analytics, data fundamentals, data structures, database management, genai foundations, llm application development, mlops, python fundamentals, rag, sql, vibe coding, visualization</t>
+  </si>
+  <si>
+    <t>ai engineering, ai product development, capstone, deployment, fullstack development, industry project, production, robotics, smart systems</t>
+  </si>
+  <si>
+    <t>ai  iot integration, computer vision, embedded systems, iot, machine learning foundations, python fundamentals</t>
+  </si>
+  <si>
+    <t>ai  iot integration, ai agents, aiops, aws, cloud, data analytics, data fundamentals, data structures, deep learning, embedded systems, genai foundations, iot, llm application development, machine learning foundations, ml foundations, mlops, python fundamentals, rag, visualization</t>
   </si>
   <si>
     <t>advanced agentic ai, ai  iot integration, ai agents, ai engineering, ai product development, aiassisted development, aiops, aws, capstone, cloud, computer vision, data analytics, data fundamentals, data structures, database management, deep learning, deployment, embedded systems, fullstack development, genai foundations, industry project, iot, llm application development, machine learning foundations, ml foundations, mlops, production, python fundamentals, rag, robotics, smart systems, sql, vibe coding, visualization</t>
   </si>
   <si>
-    <t>ai product development, aiassisted development, genai foundations, machine learning foundations, python fundamentals, vibe coding</t>
-  </si>
-  <si>
-    <t>ai  iot integration, computer vision, embedded systems, iot, machine learning foundations, python fundamentals</t>
-  </si>
-  <si>
-    <t>advanced agentic ai, ai agents, aws, cloud, deep learning, genai foundations, llm application development, ml foundations, python fundamentals, rag</t>
-  </si>
-  <si>
-    <t>ai agents, aiassisted development, aiops, data analytics, data fundamentals, data structures, database management, genai foundations, llm application development, mlops, python fundamentals, rag, sql, vibe coding, visualization</t>
-  </si>
-  <si>
-    <t>ai  iot integration, ai agents, aiops, aws, cloud, data analytics, data fundamentals, data structures, deep learning, embedded systems, genai foundations, iot, llm application development, machine learning foundations, ml foundations, mlops, python fundamentals, rag, visualization</t>
-  </si>
-  <si>
-    <t>ai engineering, ai product development, capstone, deployment, fullstack development, industry project, production, robotics, smart systems</t>
-  </si>
-  <si>
-    <t>advanced agentic ai, ai  iot integration, ai agents, embedded systems, fullstack development, genai foundations, iot, llm application development, rag</t>
-  </si>
-  <si>
-    <t>advanced analytics projects, advanced excel, business intelligence, capstone, data analytics foundations, data preparation, data visualization with python, database analytics, digital business analytics, digital marketing analytics, eda, etl, exploratory data analysis, genai tools for data analytics, graphics, industry internship, numpy, pandas, power bi, python programming for analytics, sql, statistics for data analytics, video for digital analytics</t>
-  </si>
-  <si>
-    <t>advanced excel, business intelligence, data analytics foundations, power bi, python programming for analytics, statistics for data analytics</t>
-  </si>
-  <si>
-    <t>advanced excel, business intelligence, data analytics foundations, data preparation, data visualization with python, database analytics, eda, etl, exploratory data analysis, numpy, pandas, power bi, python programming for analytics, sql, statistics for data analytics</t>
+    <t>content marketing, conversion, copywriting, digital marketing foundations, landing pages, lead generation landing pages, management, online display, remarketing, search engine marketing, sem, seo specialist track, social media marketing, strategy, website development</t>
+  </si>
+  <si>
+    <t>content marketing, conversion, copywriting, digital marketing foundations, ecommerce, google ads ecosystem discovery performance max, landing pages, lead generation landing pages, management, mobile app marketing, online display, online sales marketing, remarketing, search, search engine marketing, sem, seo specialist track, social media marketing, strategy, video marketing, website development, youtube</t>
   </si>
   <si>
     <t>aipowered digital marketing, career growth, content marketing, conversion, copywriting, digital marketing foundations, ecommerce, freelancing portfolio resume, google ads ecosystem discovery performance max, growth reputation email, interview readiness, landing pages, lead generation landing pages, management, messaging, mobile app marketing, online display, online sales marketing, remarketing, search, search engine marketing, sem, seo specialist track, social media marketing, strategy, video marketing, website development, youtube</t>
   </si>
   <si>
-    <t>content marketing, conversion, copywriting, digital marketing foundations, landing pages, lead generation landing pages, management, online display, remarketing, search engine marketing, sem, seo specialist track, social media marketing, strategy, website development</t>
-  </si>
-  <si>
-    <t>content marketing, conversion, copywriting, digital marketing foundations, ecommerce, google ads ecosystem discovery performance max, landing pages, lead generation landing pages, management, mobile app marketing, online display, online sales marketing, remarketing, search, search engine marketing, sem, seo specialist track, social media marketing, strategy, video marketing, website development, youtube</t>
+    <t>devops, cloud, aws</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/python/full-stack-python-course</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/python/advanced-full-stack-certification-course</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/python/full-stack-python-web-mobile-app-course</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/python/full-stack-gen-ai-course</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/python/full-stack-data-science-with-ai-course</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/python/full-stack-data-science-gen-ai-course</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/java/fullstack-java-course</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/java/advanced-fullstack-java-course</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/java/full-stack-java-web-mobile-app-course</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/mernstack/mern-stack-course</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/mernstack/advanced-mern-stack-course</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/mernstack/advanced-mern-stack-web-mobile-course</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/cyber-security-ethical-hacking/cyber-security-foundation-track</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/cyber-security-ethical-hacking/cyber-security-enterprise-track</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/cyber-security-ethical-hacking/cyber-security-advanced-track</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/data-analytics/data-analytics-essential</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/data-analytics/professional-data-analytics</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/data-analytics/data-analytics-for-digital-business</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/data-analytics/data-analytics-for-master</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/artificial-intelligence-with-gen-ai/genai-ai-ml-vibe-coding</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/artificial-intelligence-with-gen-ai/genai-agentic-ai-development</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/artificial-intelligence-with-gen-ai/full-stack-genai-agentic-ai-iot</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/ai-engineering-mlops-development/advanced-genai-mlops</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/ai-engineering-mlops-development/ai-software-engineer</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/ai-iot-intelligent-systems/ai-iot-program</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/ai-iot-intelligent-systems/ai-ml-genai-agentic-ai-mlops-iot</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/ai-iot-intelligent-systems/ultimate-ai-super-engineer</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/digital-marketing/digital-marketing-executive</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/digital-marketing/advanced-digital-marketing-performance</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/digital-marketing/digital-marketing-mastery-pro</t>
+  </si>
+  <si>
+    <t>https://cybrom.com/devops-cloud/cloud-devops-course</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -574,13 +689,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -873,10 +994,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -919,51 +1040,63 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>151</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>152</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -971,154 +1104,181 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="L4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>153</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>154</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F6" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="L6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>155</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="L7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>156</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>157</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L9" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>158</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F10" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="L10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>159</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1126,451 +1286,592 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="L11" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>160</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="L12" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>161</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F13" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="L13" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>162</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F14" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>163</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>16</v>
       </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="L15" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>164</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
         <v>16</v>
       </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F16" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="L16" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+        <v>165</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F17" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="L17" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <v>166</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>17</v>
       </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F18" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L18" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <v>167</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
         <v>17</v>
       </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F19" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="L19" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+        <v>168</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
         <v>17</v>
       </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F20" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="L20" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+        <v>168</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="L21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+        <v>169</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F22" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="L22" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+        <v>170</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F23" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="L23" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+        <v>171</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F24" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="L24" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+        <v>172</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E25" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F25" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="L25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+        <v>173</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F26" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="L26" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+        <v>174</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F27" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L27" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+        <v>175</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E28" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F28" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="L28" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+        <v>176</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F29" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="L29" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
+        <v>177</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D30" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E30" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F30" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="L30" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+        <v>178</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E31" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F31" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L31" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
+        <v>179</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="B32" t="s">
+        <v>28</v>
       </c>
       <c r="C32" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
-      </c>
-      <c r="E32" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="F32" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="L32" t="s">
-        <v>175</v>
+        <v>180</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="O2" r:id="rId1"/>
+    <hyperlink ref="O3" r:id="rId2"/>
+    <hyperlink ref="O4" r:id="rId3"/>
+    <hyperlink ref="O5" r:id="rId4"/>
+    <hyperlink ref="O6" r:id="rId5"/>
+    <hyperlink ref="O7" r:id="rId6"/>
+    <hyperlink ref="O8" r:id="rId7"/>
+    <hyperlink ref="O9" r:id="rId8"/>
+    <hyperlink ref="O10" r:id="rId9"/>
+    <hyperlink ref="O11" r:id="rId10"/>
+    <hyperlink ref="O12" r:id="rId11"/>
+    <hyperlink ref="O13" r:id="rId12"/>
+    <hyperlink ref="O14" r:id="rId13"/>
+    <hyperlink ref="O15" r:id="rId14"/>
+    <hyperlink ref="O16" r:id="rId15"/>
+    <hyperlink ref="O17" r:id="rId16"/>
+    <hyperlink ref="O18" r:id="rId17"/>
+    <hyperlink ref="O19" r:id="rId18"/>
+    <hyperlink ref="O20" r:id="rId19"/>
+    <hyperlink ref="O21" r:id="rId20"/>
+    <hyperlink ref="O22" r:id="rId21"/>
+    <hyperlink ref="O23" r:id="rId22"/>
+    <hyperlink ref="O24" r:id="rId23"/>
+    <hyperlink ref="O25" r:id="rId24"/>
+    <hyperlink ref="O26" r:id="rId25"/>
+    <hyperlink ref="O27" r:id="rId26"/>
+    <hyperlink ref="O28" r:id="rId27"/>
+    <hyperlink ref="O29" r:id="rId28"/>
+    <hyperlink ref="O30" r:id="rId29"/>
+    <hyperlink ref="O31" r:id="rId30"/>
+    <hyperlink ref="O32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>